--- a/test-exports/inventory-2020-01-01-to-2030-01-01.xlsx
+++ b/test-exports/inventory-2020-01-01-to-2030-01-01.xlsx
@@ -1023,184 +1023,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="KusumExport1" displayName="KusumExport1" ref="A5:T65" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A5:T65">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-    <filterColumn colId="6" hiddenButton="1"/>
-    <filterColumn colId="7" hiddenButton="1"/>
-    <filterColumn colId="8" hiddenButton="1"/>
-    <filterColumn colId="9" hiddenButton="1"/>
-    <filterColumn colId="10" hiddenButton="1"/>
-    <filterColumn colId="11" hiddenButton="1"/>
-    <filterColumn colId="12" hiddenButton="1"/>
-    <filterColumn colId="13" hiddenButton="1"/>
-    <filterColumn colId="14" hiddenButton="1"/>
-    <filterColumn colId="15" hiddenButton="1"/>
-    <filterColumn colId="16" hiddenButton="1"/>
-    <filterColumn colId="17" hiddenButton="1"/>
-    <filterColumn colId="18" hiddenButton="1"/>
-    <filterColumn colId="19" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="20">
-    <tableColumn id="1" name="Metal" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="Item name" totalsRowFunction="none"/>
-    <tableColumn id="3" name="Category" totalsRowFunction="none"/>
-    <tableColumn id="4" name="Purity" totalsRowFunction="none"/>
-    <tableColumn id="5" name="Barcode" totalsRowFunction="none"/>
-    <tableColumn id="6" name="SKU" totalsRowFunction="none"/>
-    <tableColumn id="7" name="Gross wt. (g)" totalsRowFunction="none"/>
-    <tableColumn id="8" name="Stone wt. (g)" totalsRowFunction="none"/>
-    <tableColumn id="9" name="Net wt. (g)" totalsRowFunction="none"/>
-    <tableColumn id="10" name="Stock qty" totalsRowFunction="none"/>
-    <tableColumn id="11" name="Reorder level" totalsRowFunction="none"/>
-    <tableColumn id="12" name="Purchase price" totalsRowFunction="none"/>
-    <tableColumn id="13" name="Selling price" totalsRowFunction="none"/>
-    <tableColumn id="14" name="Making basis" totalsRowFunction="none"/>
-    <tableColumn id="15" name="Making value" totalsRowFunction="none"/>
-    <tableColumn id="16" name="Status" totalsRowFunction="none"/>
-    <tableColumn id="17" name="Location" totalsRowFunction="none"/>
-    <tableColumn id="18" name="Batch doc no." totalsRowFunction="none"/>
-    <tableColumn id="19" name="Created date" totalsRowFunction="none"/>
-    <tableColumn id="20" name="Notes" totalsRowFunction="none"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" name="KusumExport2" displayName="KusumExport2" ref="A6:I12" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A6:I12">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-    <filterColumn colId="6" hiddenButton="1"/>
-    <filterColumn colId="7" hiddenButton="1"/>
-    <filterColumn colId="8" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="9">
-    <tableColumn id="1" name="Metal" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="Item name" totalsRowFunction="none"/>
-    <tableColumn id="3" name="Category" totalsRowFunction="none"/>
-    <tableColumn id="4" name="Purity" totalsRowFunction="none"/>
-    <tableColumn id="5" name="Barcode records" totalsRowFunction="none"/>
-    <tableColumn id="6" name="Stock pieces" totalsRowFunction="none"/>
-    <tableColumn id="7" name="Gross wt. (g)" totalsRowFunction="none"/>
-    <tableColumn id="8" name="Net wt. (g)" totalsRowFunction="none"/>
-    <tableColumn id="9" name="Total value" totalsRowFunction="none"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" name="KusumExport3" displayName="KusumExport3" ref="A5:T40" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A5:T40">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-    <filterColumn colId="6" hiddenButton="1"/>
-    <filterColumn colId="7" hiddenButton="1"/>
-    <filterColumn colId="8" hiddenButton="1"/>
-    <filterColumn colId="9" hiddenButton="1"/>
-    <filterColumn colId="10" hiddenButton="1"/>
-    <filterColumn colId="11" hiddenButton="1"/>
-    <filterColumn colId="12" hiddenButton="1"/>
-    <filterColumn colId="13" hiddenButton="1"/>
-    <filterColumn colId="14" hiddenButton="1"/>
-    <filterColumn colId="15" hiddenButton="1"/>
-    <filterColumn colId="16" hiddenButton="1"/>
-    <filterColumn colId="17" hiddenButton="1"/>
-    <filterColumn colId="18" hiddenButton="1"/>
-    <filterColumn colId="19" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="20">
-    <tableColumn id="1" name="Metal" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="Item name" totalsRowFunction="none"/>
-    <tableColumn id="3" name="Category" totalsRowFunction="none"/>
-    <tableColumn id="4" name="Purity" totalsRowFunction="none"/>
-    <tableColumn id="5" name="Barcode" totalsRowFunction="none"/>
-    <tableColumn id="6" name="SKU" totalsRowFunction="none"/>
-    <tableColumn id="7" name="Gross wt. (g)" totalsRowFunction="none"/>
-    <tableColumn id="8" name="Stone wt. (g)" totalsRowFunction="none"/>
-    <tableColumn id="9" name="Net wt. (g)" totalsRowFunction="none"/>
-    <tableColumn id="10" name="Stock qty" totalsRowFunction="none"/>
-    <tableColumn id="11" name="Reorder level" totalsRowFunction="none"/>
-    <tableColumn id="12" name="Purchase price" totalsRowFunction="none"/>
-    <tableColumn id="13" name="Selling price" totalsRowFunction="none"/>
-    <tableColumn id="14" name="Making basis" totalsRowFunction="none"/>
-    <tableColumn id="15" name="Making value" totalsRowFunction="none"/>
-    <tableColumn id="16" name="Status" totalsRowFunction="none"/>
-    <tableColumn id="17" name="Location" totalsRowFunction="none"/>
-    <tableColumn id="18" name="Batch doc no." totalsRowFunction="none"/>
-    <tableColumn id="19" name="Created date" totalsRowFunction="none"/>
-    <tableColumn id="20" name="Notes" totalsRowFunction="none"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" name="KusumExport4" displayName="KusumExport4" ref="A5:T30" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A5:T30">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-    <filterColumn colId="6" hiddenButton="1"/>
-    <filterColumn colId="7" hiddenButton="1"/>
-    <filterColumn colId="8" hiddenButton="1"/>
-    <filterColumn colId="9" hiddenButton="1"/>
-    <filterColumn colId="10" hiddenButton="1"/>
-    <filterColumn colId="11" hiddenButton="1"/>
-    <filterColumn colId="12" hiddenButton="1"/>
-    <filterColumn colId="13" hiddenButton="1"/>
-    <filterColumn colId="14" hiddenButton="1"/>
-    <filterColumn colId="15" hiddenButton="1"/>
-    <filterColumn colId="16" hiddenButton="1"/>
-    <filterColumn colId="17" hiddenButton="1"/>
-    <filterColumn colId="18" hiddenButton="1"/>
-    <filterColumn colId="19" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="20">
-    <tableColumn id="1" name="Metal" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="Item name" totalsRowFunction="none"/>
-    <tableColumn id="3" name="Category" totalsRowFunction="none"/>
-    <tableColumn id="4" name="Purity" totalsRowFunction="none"/>
-    <tableColumn id="5" name="Barcode" totalsRowFunction="none"/>
-    <tableColumn id="6" name="SKU" totalsRowFunction="none"/>
-    <tableColumn id="7" name="Gross wt. (g)" totalsRowFunction="none"/>
-    <tableColumn id="8" name="Stone wt. (g)" totalsRowFunction="none"/>
-    <tableColumn id="9" name="Net wt. (g)" totalsRowFunction="none"/>
-    <tableColumn id="10" name="Stock qty" totalsRowFunction="none"/>
-    <tableColumn id="11" name="Reorder level" totalsRowFunction="none"/>
-    <tableColumn id="12" name="Purchase price" totalsRowFunction="none"/>
-    <tableColumn id="13" name="Selling price" totalsRowFunction="none"/>
-    <tableColumn id="14" name="Making basis" totalsRowFunction="none"/>
-    <tableColumn id="15" name="Making value" totalsRowFunction="none"/>
-    <tableColumn id="16" name="Status" totalsRowFunction="none"/>
-    <tableColumn id="17" name="Location" totalsRowFunction="none"/>
-    <tableColumn id="18" name="Batch doc no." totalsRowFunction="none"/>
-    <tableColumn id="19" name="Created date" totalsRowFunction="none"/>
-    <tableColumn id="20" name="Notes" totalsRowFunction="none"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5172,9 +4994,6 @@
     <oddFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</evenFooter>
   </headerFooter>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -5480,9 +5299,6 @@
     <oddFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</evenFooter>
   </headerFooter>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -7703,9 +7519,6 @@
     <oddFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</evenFooter>
   </headerFooter>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -9330,8 +9143,5 @@
     <oddFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</evenFooter>
   </headerFooter>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>